--- a/payment_forms/008_season_pass_access_form--payment_forms.xlsx
+++ b/payment_forms/008_season_pass_access_form--payment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'credit_card',_'label':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'credit_card', 'label': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'season_pass',_'label':_'season_pass'}</t>
+          <t>season_pass</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'season_pass', 'label': 'Season Pass'}</t>
+          <t>Season Pass</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'guest_pass',_'label':_'guest_pass'}</t>
+          <t>guest_pass</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'guest_pass', 'label': 'Guest Pass'}</t>
+          <t>Guest Pass</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'membership_pass',_'label':_'membership_pass'}</t>
+          <t>membership_pass</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'membership_pass', 'label': 'Membership Pass'}</t>
+          <t>Membership Pass</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'january',_'label':_'january'}</t>
+          <t>january</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'january', 'label': 'January'}</t>
+          <t>January</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'february',_'label':_'february'}</t>
+          <t>february</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'february', 'label': 'February'}</t>
+          <t>February</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'march',_'label':_'march'}</t>
+          <t>march</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'march', 'label': 'March'}</t>
+          <t>March</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'april',_'label':_'april'}</t>
+          <t>april</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'april', 'label': 'April'}</t>
+          <t>April</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'may',_'label':_'may'}</t>
+          <t>may</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'may', 'label': 'May'}</t>
+          <t>May</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'june',_'label':_'june'}</t>
+          <t>june</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'june', 'label': 'June'}</t>
+          <t>June</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'july',_'label':_'july'}</t>
+          <t>july</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'july', 'label': 'July'}</t>
+          <t>July</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'august',_'label':_'august'}</t>
+          <t>august</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'august', 'label': 'August'}</t>
+          <t>August</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'september',_'label':_'september'}</t>
+          <t>september</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'september', 'label': 'September'}</t>
+          <t>September</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'june',_'label':_'june'}</t>
+          <t>june</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'june', 'label': 'June'}</t>
+          <t>June</t>
         </is>
       </c>
     </row>
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'july',_'label':_'july'}</t>
+          <t>july</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'july', 'label': 'July'}</t>
+          <t>July</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'august',_'label':_'august'}</t>
+          <t>august</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'august', 'label': 'August'}</t>
+          <t>August</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'september',_'label':_'september'}</t>
+          <t>september</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'september', 'label': 'September'}</t>
+          <t>September</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'abc_corp',_'label':_'abc_corp'}</t>
+          <t>abc_corp</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'abc corp', 'label': 'ABC Corp'}</t>
+          <t>ABC Corp</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'def_corp',_'label':_'def_corp'}</t>
+          <t>def_corp</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'def corp', 'label': 'DEF Corp'}</t>
+          <t>DEF Corp</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'ghi_corp',_'label':_'ghi_corp'}</t>
+          <t>ghi_corp</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'ghi corp', 'label': 'GHI Corp'}</t>
+          <t>GHI Corp</t>
         </is>
       </c>
     </row>
